--- a/virtual-physics-lab/app/dl/EJC_Q2_thermistor_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/EJC_Q2_thermistor_dataset.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -95,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +106,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -686,169 +689,169 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>5.8</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>7.8</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>10.1</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>18.2</v>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>32.7</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>42.3</v>
       </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -940,21 +943,21 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>B6/(C6/1000)</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>B6*C6/1000</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>IF(A7&lt;&gt;"",0.5*(E6+B7*C7/1000)*(A7-A6),"")</f>
         <v/>
       </c>
@@ -963,7 +966,7 @@
           <t>P at t = 90 s</t>
         </is>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>E9</f>
         <v/>
       </c>
@@ -977,21 +980,21 @@
       <c r="A7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>B7/(C7/1000)</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>B7*C7/1000</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>IF(A8&lt;&gt;"",0.5*(E7+B8*C8/1000)*(A8-A7),"")</f>
         <v/>
       </c>
@@ -1000,7 +1003,7 @@
           <t>total energy = Σ strips</t>
         </is>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
@@ -1014,21 +1017,21 @@
       <c r="A8" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>5.8</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>B8/(C8/1000)</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>B8*C8/1000</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>IF(A9&lt;&gt;"",0.5*(E8+B9*C9/1000)*(A9-A8),"")</f>
         <v/>
       </c>
@@ -1037,25 +1040,25 @@
       <c r="A9" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>7.8</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>B9/(C9/1000)</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>B9*C9/1000</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>IF(A10&lt;&gt;"",0.5*(E9+B10*C10/1000)*(A10-A9),"")</f>
         <v/>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Energy uses the trapezium rule on the P–t data (Δt = 30 s).</t>
         </is>
@@ -1065,21 +1068,21 @@
       <c r="A10" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>10.1</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>B10/(C10/1000)</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>B10*C10/1000</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>IF(A11&lt;&gt;"",0.5*(E10+B11*C11/1000)*(A11-A10),"")</f>
         <v/>
       </c>
@@ -1088,21 +1091,21 @@
       <c r="A11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>B11/(C11/1000)</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>B11*C11/1000</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>IF(A12&lt;&gt;"",0.5*(E11+B12*C12/1000)*(A12-A11),"")</f>
         <v/>
       </c>
@@ -1111,21 +1114,21 @@
       <c r="A12" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>B12/(C12/1000)</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>B12*C12/1000</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f>IF(A13&lt;&gt;"",0.5*(E12+B13*C13/1000)*(A13-A12),"")</f>
         <v/>
       </c>
@@ -1134,21 +1137,21 @@
       <c r="A13" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>18.2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f>B13/(C13/1000)</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <f>B13*C13/1000</f>
         <v/>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <f>IF(A14&lt;&gt;"",0.5*(E13+B14*C14/1000)*(A14-A13),"")</f>
         <v/>
       </c>
@@ -1157,21 +1160,21 @@
       <c r="A14" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <f>B14/(C14/1000)</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>B14*C14/1000</f>
         <v/>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <f>IF(A15&lt;&gt;"",0.5*(E14+B15*C15/1000)*(A15-A14),"")</f>
         <v/>
       </c>
@@ -1180,21 +1183,21 @@
       <c r="A15" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f>B15/(C15/1000)</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>B15*C15/1000</f>
         <v/>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <f>IF(A16&lt;&gt;"",0.5*(E15+B16*C16/1000)*(A16-A15),"")</f>
         <v/>
       </c>
@@ -1203,21 +1206,21 @@
       <c r="A16" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>32.7</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <f>B16/(C16/1000)</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>B16*C16/1000</f>
         <v/>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <f>IF(A17&lt;&gt;"",0.5*(E16+B17*C17/1000)*(A17-A16),"")</f>
         <v/>
       </c>
@@ -1226,21 +1229,21 @@
       <c r="A17" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>42.3</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f>B17/(C17/1000)</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>B17*C17/1000</f>
         <v/>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <f>IF(A18&lt;&gt;"",0.5*(E17+B18*C18/1000)*(A18-A17),"")</f>
         <v/>
       </c>
